--- a/data/vendor-search/results_all_gameconsoles.xlsx
+++ b/data/vendor-search/results_all_gameconsoles.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,6 +488,11 @@
           <t>cpe:2.3:a:valve_software:half-life_dedicated_server:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,6 +524,11 @@
           <t>cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.3:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -545,6 +560,11 @@
           <t>cpe:2.3:a:sierra:half-life:*:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,6 +596,11 @@
           <t>cpe:2.3:a:sierra:half-life:*:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -607,6 +632,11 @@
           <t>cpe:2.3:a:valve_software:half-life:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,6 +668,11 @@
           <t>cpe:2.3:a:valve_software:half-life:1.1.0.4:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life:1.1.0.4:*:windows:*:*:*:*:*|cpe:2.3:a:valve_software:half-life:1.1.0.8:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life:1.1.0.9:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life:1.1.1.0:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:*:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.3:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -669,6 +704,11 @@
           <t>cpe:2.3:a:valve_software:half-life_cstrike_dedicated_server:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -704,6 +744,11 @@
           <t>cpe:2.3:a:amxmod.net:amx_mod:0.9.2:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -735,6 +780,11 @@
           <t>cpe:2.3:a:valve_software:half-life:1.1.0.4:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life:1.1.0.4:*:windows:*:*:*:*:*|cpe:2.3:a:valve_software:half-life:1.1.0.8:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life:1.1.0.9:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life:1.1.1.0:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.0.4:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.0.5:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.0.6:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.0.7:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.0.8:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.0.9:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.1.0:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.1.1c1:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.1.1d:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.1.1e:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.1.1e:*:win32:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:3.1.3:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:4.1.0.4:*:win32:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:4.1.0.6:*:win32:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:4.1.0.7:*:win32:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:4.1.0.8:*:win32:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:4.1.0.9:*:win32:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:4.1.1.0:*:win32:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:4.1.1.1c1:*:win32:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:4.1.1.1d_beta:*:win32:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:4.1.1.1e:*:linux:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:4.1.1.1e:*:win32:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -766,6 +816,11 @@
           <t>cpe:2.3:h:sony:playstation_portable:2.0_firmware:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>playstation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -801,6 +856,11 @@
           <t>cpe:2.3:a:todd_miller:sudo:1.6:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.1:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.2:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3_p1:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3_p2:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3_p3:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3_p4:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3_p5:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3_p6:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3_p7:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3p1:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3p2:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3p3:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3p4:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3p5:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3p6:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.3p7:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.4:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.4_p1:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.4_p2:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.4p1:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.4p2:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.5:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.5_p1:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.5_p2:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.5p1:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.5p2:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.6:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.7:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.7_p5:*:*:*:*:*:*:*|cpe:2.3:a:todd_miller:sudo:1.6.8:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -836,6 +896,11 @@
           <t>cpe:2.3:a:valve_software:half-life_cstrike_dedicated_server:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -867,6 +932,11 @@
           <t>cpe:2.3:h:sony:playstation_portable:2.00:*:*:*:*:*:*:*|cpe:2.3:h:sony:playstation_portable:2.10:*:*:*:*:*:*:*|cpe:2.3:h:sony:playstation_portable:2.20:*:*:*:*:*:*:*|cpe:2.3:h:sony:playstation_portable:2.30:*:*:*:*:*:*:*|cpe:2.3:h:sony:playstation_portable:2.40:*:*:*:*:*:*:*|cpe:2.3:h:sony:playstation_portable:2.50:*:*:*:*:*:*:*|cpe:2.3:h:sony:playstation_portable:2.60:*:*:*:*:*:*:*|cpe:2.3:h:sony:playstation_portable:2.70:*:*:*:*:*:*:*|cpe:2.3:h:sony:playstation_portable:2.80:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>playstation</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -902,6 +972,11 @@
           <t>cpe:2.3:a:apache:tomcat:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -937,6 +1012,11 @@
           <t>cpe:2.3:h:sony:playstation_3:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>playstation|ps3</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -972,6 +1052,11 @@
           <t>cpe:2.3:a:gnu:bash:*:*:*:*:*:*:*:*|cpe:2.3:o:fedoraproject:fedora:23:*:*:*:*:*:*:*|cpe:2.3:o:fedoraproject:fedora:24:*:*:*:*:*:*:*|cpe:2.3:o:fedoraproject:fedora:25:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1007,6 +1092,11 @@
           <t>cpe:2.3:o:valvesoftware:steamos:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1042,6 +1132,11 @@
           <t>cpe:2.3:a:cloudera:manager:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1077,6 +1172,11 @@
           <t>cpe:2.3:a:sony:content_manager_assistant:*:*:*:*:*:*:playstation:*</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>playstation</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1108,6 +1208,11 @@
           <t>cpe:2.3:o:valvesoftware:steam_link_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:valvesoftware:steam_link:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1143,6 +1248,11 @@
           <t>cpe:2.3:o:valvesoftware:steam_link_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:valvesoftware:steam_link:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1178,6 +1288,11 @@
           <t>cpe:2.3:a:wireshark:wireshark:*:*:*:*:*:*:*:*|cpe:2.3:o:debian:debian_linux:9.0:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1213,6 +1328,11 @@
           <t>cpe:2.3:a:valvesoftware:steam_client:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1244,6 +1364,11 @@
           <t>cpe:2.3:a:valvesoftware:dota_2:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1275,6 +1400,11 @@
           <t>cpe:2.3:a:valvesoftware:dota_2:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1310,6 +1440,11 @@
           <t>cpe:2.3:a:valvesoftware:dota_2:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1341,6 +1476,11 @@
           <t>cpe:2.3:a:valvesoftware:dota_2:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1376,6 +1516,11 @@
           <t>cpe:2.3:o:omron:plc_cj_firmware:*:*:*:*:*:*:*:*|cpe:2.3:o:omron:plc_cs_firmware:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1411,6 +1556,11 @@
           <t>cpe:2.3:a:guzzlephp:guzzle:*:*:*:*:*:*:*:*|cpe:2.3:o:debian:debian_linux:11.0:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1442,6 +1592,11 @@
           <t>cpe:2.3:o:microsoft:windows_10:20h2:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10:21h1:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10:21h2:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1477,6 +1632,11 @@
           <t>cpe:2.3:o:nintendo:wi-fi_network_adaptor_wap_001_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:nintendo:wi-fi_network_adaptor_wap_001:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>nintendo</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1512,6 +1672,11 @@
           <t>cpe:2.3:o:nintendo:wi-fi_network_adaptor_wap_001_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:nintendo:wi-fi_network_adaptor_wap_001:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>nintendo</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1547,6 +1712,11 @@
           <t>cpe:2.3:o:sony:playstation_4_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:playstation_4:-:*:*:*:*:*:*:*|cpe:2.3:o:sony:playstation_5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sony:playstation_5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>playstation|ps5|ps4</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1582,6 +1752,11 @@
           <t>cpe:2.3:a:wfs:heaven_burns_red:*:*:*:*:*:steam:*:*</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1617,6 +1792,11 @@
           <t>cpe:2.3:a:nintendo:animal_crossing\:_new_horizons:*:*:*:*:*:*:*:*|cpe:2.3:a:nintendo:arms:*:*:*:*:*:*:*:*|cpe:2.3:a:nintendo:mario_kart_7:*:*:*:*:*:*:*:*|cpe:2.3:a:nintendo:mario_kart_8:*:*:*:*:deluxe:*:*:*|cpe:2.3:a:nintendo:mario_kart_8:-:*:*:*:-:*:*:*|cpe:2.3:a:nintendo:splatoon:*:*:*:*:*:*:*:*|cpe:2.3:a:nintendo:splatoon_2:*:*:*:*:*:*:*:*|cpe:2.3:a:nintendo:splatoon_3:*:*:*:*:*:*:*:*|cpe:2.3:a:nintendo:super_mario_maker_2:*:*:*:*:*:*:*:*|cpe:2.3:a:nintendo:switch_sports:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>nintendo switch|nintendo</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1652,6 +1832,11 @@
           <t>cpe:2.3:a:wfs:another_eden:*:*:*:*:global:steam:*:*|cpe:2.3:a:wfs:another_eden:*:*:*:*:japanese:windows:*:*</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1687,6 +1872,11 @@
           <t>cpe:2.3:a:valvesoftware:half-life:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1722,6 +1912,11 @@
           <t>cpe:2.3:a:valvesoftware:counter-strike:8684:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1757,6 +1952,11 @@
           <t>cpe:2.3:o:microsoft:windows_10_21h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10_22h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11_21h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11_22h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11_23h2:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1790,6 +1990,11 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>cpe:2.3:o:microsoft:windows_11_21h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11_22h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11_23h2:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>xbox</t>
         </is>
       </c>
     </row>
@@ -1879,6 +2084,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.12:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.12:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.12:rc3:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.12:rc4:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.12:rc5:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1910,6 +2120,11 @@
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>nintendo</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1945,6 +2160,11 @@
           <t>cpe:2.3:a:valve_software:half-life_dedicated_server:*:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:webmod_plugin:0.48:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1980,6 +2200,11 @@
           <t>cpe:2.3:a:amxmodx:amx_mod_x:1.76d:*:*:*:*:*:*:*|cpe:2.3:a:valve_software:half-life_dedicated_server:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2015,6 +2240,11 @@
           <t>cpe:2.3:o:valvesoftware:steamos:-:beta:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2050,6 +2280,11 @@
           <t>cpe:2.3:a:valvesoftware:steam_client:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2085,6 +2320,11 @@
           <t>cpe:2.3:a:schneider-electric:device_type_manager:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2120,6 +2360,11 @@
           <t>cpe:2.3:a:valvesoftware:steam_client:2.10.91.91:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2155,6 +2400,11 @@
           <t>cpe:2.3:a:activision:call_of_duty\:_advanced_warfare:-:*:*:*:*:*:*:*|cpe:2.3:a:activision:call_of_duty\:_black_ops_1:-:*:*:*:*:*:*:*|cpe:2.3:a:activision:call_of_duty\:_blacks_ops_2:-:*:*:*:*:*:*:*|cpe:2.3:a:activision:call_of_duty\:_ghosts:-:*:*:*:*:*:*:*|cpe:2.3:a:activision:call_of_duty\:_modern_warfare_2:-:*:*:*:*:*:*:*|cpe:2.3:a:activision:call_of_duty\:_modern_warfare_3:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2190,6 +2440,11 @@
           <t>cpe:2.3:a:valvesoftware:steam_client:1528829181:beta:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2225,6 +2480,11 @@
           <t>cpe:2.3:a:valvesoftware:steam_client:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2260,6 +2520,11 @@
           <t>cpe:2.3:a:valvesoftware:steam_client:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2295,6 +2560,11 @@
           <t>cpe:2.3:a:imagemagick:imagemagick:7.0.8-43:*:*:*:*:*:*:*|cpe:2.3:o:opensuse:leap:15.0:*:*:*:*:*:*:*|cpe:2.3:o:opensuse:leap:15.1:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ps3</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2330,6 +2600,11 @@
           <t>cpe:2.3:a:valvesoftware:steam_client:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2365,6 +2640,11 @@
           <t>cpe:2.3:o:vzug:combi-stream_mslq_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:vzug:combi-stream_mslq:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2400,6 +2680,11 @@
           <t>cpe:2.3:o:vzug:combi-stream_mslq_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:vzug:combi-stream_mslq:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2435,6 +2720,11 @@
           <t>cpe:2.3:o:vzug:combi-stream_mslq_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:vzug:combi-stream_mslq:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2470,6 +2760,11 @@
           <t>cpe:2.3:o:vzug:combi-stream_mslq_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:vzug:combi-stream_mslq:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2505,6 +2800,11 @@
           <t>cpe:2.3:o:vzug:combi-stream_mslq_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:vzug:combi-stream_mslq:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2540,6 +2840,11 @@
           <t>cpe:2.3:a:valvesoftware:dota_2:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2575,6 +2880,11 @@
           <t>cpe:2.3:a:valvesoftware:source:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2610,6 +2920,11 @@
           <t>cpe:2.3:a:seta:morita_shogi_64:*:*:*:*:*:*:*:*|cpe:2.3:h:nintendo:nintendo_64:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>nintendo</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2645,6 +2960,11 @@
           <t>cpe:2.3:a:ui:unifi_controller:-:*:*:*:*:*:*:*|cpe:2.3:a:w1.fi:hostapd:*:*:*:*:*:*:*:*|cpe:2.3:h:asus:rt-n11:-:*:*:*:*:*:*:*|cpe:2.3:h:broadcom:adsl:-:*:*:*:*:*:*:*|cpe:2.3:h:canon:selphy_cp1200:-:*:*:*:*:*:*:*|cpe:2.3:h:cisco:wap131:-:*:*:*:*:*:*:*|cpe:2.3:h:cisco:wap150:-:*:*:*:*:*:*:*|cpe:2.3:h:cisco:wap351:-:*:*:*:*:*:*:*|cpe:2.3:h:dlink:dvg-n5412sp:-:*:*:*:*:*:*:*|cpe:2.3:h:dell:b1165nfw:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:ep-101:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:ew-m970a3t:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:m571t:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-100:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-2101:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-2105:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-241:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-320:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-330:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-340:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-4100:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-4105:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-440:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-620:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-630:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-702:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-8500:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-8600:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-960:-:*:*:*:*:*:*:*|cpe:2.3:h:epson:xp-970:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:5020_z4a69a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:5030_m2u92b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:5030_z4a70a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:5034_z4a74a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:5660_f8b04a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_3456_a9t84c:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_3545_a9t81a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_3545_a9t81c:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_3545_a9t83b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_3546_a9t82a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_3548_a9t81b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4515:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4518:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4535_f0v64a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4535_f0v64b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4535_f0v64c:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4536_f0v65a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4538_f0v66b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4675_f1h97a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4675_f1h97b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4675_f1h97c:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4676_f1h98a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_4678_f1h99b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_5575_g0v48b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:deskjet_ink_advantage_5575_g0v48c:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_100_cn517a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_100_cn517b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_100_cn517c:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_100_cn518a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_100_cn519a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_100_cn519b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_110_cq809a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_110_cq809b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_110_cq809c:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_110_cq809d:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_110_cq812c:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_111_cq810a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_114_cq811a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_114_cq811b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_114_cq812a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_120_cz022a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_120_cz022b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_120_cz022c:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4500_a9t80a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4500_a9t80b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4500_a9t89a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4500_d3p93a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4501_c8d05a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4502_a9t85a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4502_a9t87b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4503_e6g71b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4504_a9t88b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4504_c8d04a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4505_a9t86a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4507_e6g70b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4508_e6g72b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4509_d3p94a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4509_d3p94b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4511_k9h50a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4512_k9h49a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4513_k9h51a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4516_k9h52a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4520_e6g67a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4520_e6g67b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4520_f0v63a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4520_f0v63b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4520_f0v69a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4521_k9t10b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4522_f0v67a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4523_j6u60b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4524_f0v71b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4524_f0v72b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4524_k9t01a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4525_k9t09b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4526_k9t05b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4527_j6u61b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_4528_k9t08b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5000_m2u85a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5000_m2u85b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5000_m2u91a:*:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5000_m2u91a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5000_m2u94b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5000_z4a54a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5000_z4a74a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5020_m2u91b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5530:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5531:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5532:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5534:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5535:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5536:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5539:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5540_f2e72a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5540_g0v47a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5540_g0v51a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5540_g0v52a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5540_g0v53a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5540_k7c85a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5541_k7g89a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5542_k7c88a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5543_n9u88a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5544_k7c89a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5544_k7c93a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5545_g0v50a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5546_k7c90a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5547_j6u64a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5548_k7g87a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5640_b9s56a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5640_b9s58a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5642_b9s64a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5643_b9s63a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5644_b9s65a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5646_f8b05a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5664_f8b08a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_5665_f8b06a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_6020_5se16b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_6020_5se17a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_6020_6wd35a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_6020_7cz37a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_6052_5se18a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_6055_5se16a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_6540_b9s59a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_7640:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_7644_e4w46a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_7645_e4w44a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6200_k7g18a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6200_k7g26b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6200_k7s21b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6200_y0k13d_:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6200_y0k15a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6220_k7g20d:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6220_k7g21b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6222_y0k13d:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6222_y0k14d:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6230_k7g25b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6232_k7g26b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6234_k7s21b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_6252_k7g22a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7100_3xd89a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7100_k7g93a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7100_k7g99a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7100_z3m37a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7100_z3m52a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7120_z3m41d:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7155_z3m52a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7164_k7g99a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7800_k7r96a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7800_k7s00a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7800_k7s10d:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7800_y0g42d:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7800_y0g52b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7822_y0g42d:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7822_y0g43d:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_photo_7830_y0g50b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_pro_6420_5se45b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_pro_6420_5se46a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_pro_6420_6wd14a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_pro_6420_6wd16a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_pro_6452_5se47a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:envy_pro_6455_5se45a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4650_e6g87a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4650_f1h96a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4650_f1h96b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4652_f1j02a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4652_f1j05b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4652_k9v84b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4654_f1j06b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4654_f1j07b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4655_f1j00a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4655_k9v79a:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4655_k9v82b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4656_k9v81b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4657_v6d29b:-:*:*:*:*:*:*:*|cpe:2.3:h:hp:officejet_4658_v6d30b:-:*:*:*:*:*:*:*|cpe:2.3:h:huawei:hg255s:-:*:*:*:*:*:*:*|cpe:2.3:h:huawei:hg532e:-:*:*:*:*:*:*:*|cpe:2.3:h:nec:wr8165n:-:*:*:*:*:*:*:*|cpe:2.3:h:netgear:wnhde111:-:*:*:*:*:*:*:*|cpe:2.3:h:ruckussecurity:zonedirector_1200:-:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:archer_c50:-:*:*:*:*:*:*:*|cpe:2.3:h:zte:zxv10_w300:-:*:*:*:*:*:*:*|cpe:2.3:h:zyxel:amg1202-t10b:-:*:*:*:*:*:*:*|cpe:2.3:h:zyxel:vmg8324-b10a:-:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10:-:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:xbox_one:10.0.19041.2494:*:*:*:*:*:*:*|cpe:2.3:o:fedoraproject:fedora:31:*:*:*:*:*:*:*|cpe:2.3:o:fedoraproject:fedora:32:*:*:*:*:*:*:*|cpe:2.3:o:debian:debian_linux:9.0:*:*:*:*:*:*:*|cpe:2.3:o:debian:debian_linux:10.0:*:*:*:*:*:*:*|cpe:2.3:o:canonical:ubuntu_linux:20.04:*:*:*:lts:*:*:*</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2680,6 +3000,11 @@
           <t>cpe:2.3:a:valvesoftware:steam_client:2.10.91.91:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2715,6 +3040,11 @@
           <t>cpe:2.3:a:valvesoftware:game_networking_sockets:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2750,6 +3080,11 @@
           <t>cpe:2.3:a:valvesoftware:game_networking_sockets:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2785,6 +3120,11 @@
           <t>cpe:2.3:a:valvesoftware:game_networking_sockets:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2820,6 +3160,11 @@
           <t>cpe:2.3:a:valvesoftware:game_networking_sockets:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2855,6 +3200,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2890,6 +3240,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2925,6 +3280,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2960,6 +3320,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2995,6 +3360,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3030,6 +3400,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3065,6 +3440,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3100,6 +3480,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3135,6 +3520,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3170,6 +3560,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3205,6 +3600,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3240,6 +3640,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3275,6 +3680,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3310,6 +3720,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3345,6 +3760,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3380,6 +3800,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3415,6 +3840,11 @@
           <t>cpe:2.3:o:asus:asmb9-ikvm_firmware:1.11.12:*:*:*:*:*:*:*|cpe:2.3:h:asus:asmb9-ikvm:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24-e_firmware:1.10.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4_firmware:1.10.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs4_firmware:1.09:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4x_firmware:1.11.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4x:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700-e9-rs12_firmware:1.11.5:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700-e9-rs12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs100-e10-pi2_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs100-e10-pi2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-ps4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs300-e10-rs4_firmware:1.13.6:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs300-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-ps4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9-rs4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e9_rs4_u_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e9_rs4_u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:e700_g4_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:e700_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c422_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c422_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_x299_pro\/se_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_x299_pro\/se:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-u12\/10g-2s_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-u12\/10g-2s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:knpa-u16_firmware:1.13.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:knpa-u16:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_dhd_g4_firmware:1.13.7:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_dhd_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc4000_g4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc4000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs24-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs24-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720q-e9-rs8-s_firmware:1.15.0:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720q-e9-rs8-s:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pa-d8c_firmware:1.14.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pa-d8c:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs24-u_firmware:1.14.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs24-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs8-g_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs8-g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-ps4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:pro_e800_g4_firmware:1.14.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:pro_e800_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500-e9-rs4-u_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500-e9-rs4-u:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs12-e_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs520-e9-rs8_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs520-e9-rs8:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:esc8000_g4\/10g_firmware:1.15.4:*:*:*:*:*:*:*|cpe:2.3:h:asus:esc8000_g4\/10g:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720-e9-rs12-e_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720-e9-rs12-e:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:ws_c621e_sage_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:ws_c621e_sage:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-ps4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-ps4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs500a-e10-rs4_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs500a-e10-rs4:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs12v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs700a-e9-rs4v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs700a-e9-rs4v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs12v2_firmware:1.15.2:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs12v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:rs720a-e9-rs24v2_firmware:1.15.1:*:*:*:*:*:*:*|cpe:2.3:h:asus:rs720a-e9-rs24v2:-:*:*:*:*:*:*:*|cpe:2.3:o:asus:z11pr-d16_firmware:1.15.3:*:*:*:*:*:*:*|cpe:2.3:h:asus:z11pr-d16:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3450,6 +3880,11 @@
           <t>cpe:2.3:a:valvesoftware:steam_client:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3485,6 +3920,11 @@
           <t>cpe:2.3:a:archisteamfarm_project:archisteamfarm:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3520,6 +3960,11 @@
           <t>cpe:2.3:a:archisteamfarm_project:archisteamfarm:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3555,6 +4000,11 @@
           <t>cpe:2.3:a:steam_group_viewer_project:steam_group_viewer:*:*:*:*:*:wordpress:*:*</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3590,6 +4040,11 @@
           <t>cpe:2.3:a:archisteamfarm_project:archisteamfarm:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3621,6 +4076,11 @@
           <t>cpe:2.3:o:microsoft:windows_10:-:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10:20h2:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10:21h1:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10:21h2:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10:1607:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10:1809:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10:1909:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11:-:*:*:*:*:*:arm64:*|cpe:2.3:o:microsoft:windows_11:-:*:*:*:*:*:x64:*</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3656,6 +4116,11 @@
           <t>cpe:2.3:a:nintendo:mario_kart_wii:rmce01:*:*:*:*:*:*:*|cpe:2.3:a:nintendo:mario_kart_wii:rmcj01:*:*:*:*:*:*:*|cpe:2.3:a:nintendo:mario_kart_wii:rmck01:*:*:*:*:*:*:*|cpe:2.3:a:nintendo:mario_kart_wii:rmcp01:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>nintendo</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3691,6 +4156,11 @@
           <t>cpe:2.3:a:moonlight-stream:moonlight-common-c:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight:*:*:*:*:*:iphone_os:*:*|cpe:2.3:a:moonlight-stream:moonlight:*:*:*:*:*:tvos:*:*|cpe:2.3:a:moonlight-stream:moonlight:*:*:*:*:*:android:*:*|cpe:2.3:a:moonlight-stream:moonlight:0.10.22:*:*:*:*:chrome:*:*|cpe:2.3:a:moonlight-stream:moonlight_embedded:2.6.0:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_xbox:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_tv:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_switch:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_vita:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3726,6 +4196,11 @@
           <t>cpe:2.3:a:moonlight-stream:moonlight-common-c:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight:*:*:*:*:*:iphone_os:*:*|cpe:2.3:a:moonlight-stream:moonlight:*:*:*:*:*:tvos:*:*|cpe:2.3:a:moonlight-stream:moonlight:*:*:*:*:*:android:*:*|cpe:2.3:a:moonlight-stream:moonlight:0.10.22:*:*:*:*:chrome:*:*|cpe:2.3:a:moonlight-stream:moonlight_embedded:2.6.0:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_xbox:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_tv:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_switch:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_vita:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3761,6 +4236,11 @@
           <t>cpe:2.3:a:moonlight-stream:moonlight-common-c:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight:*:*:*:*:*:iphone_os:*:*|cpe:2.3:a:moonlight-stream:moonlight:*:*:*:*:*:tvos:*:*|cpe:2.3:a:moonlight-stream:moonlight:*:*:*:*:*:android:*:*|cpe:2.3:a:moonlight-stream:moonlight:*:*:*:*:*:chrome:*:*|cpe:2.3:a:moonlight-stream:moonlight_embedded:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_xbox:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_tv:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_switch:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_vita:*:*:*:*:*:*:*:*|cpe:2.3:a:moonlight-stream:moonlight_qt\/pc:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3792,6 +4272,11 @@
           <t>cpe:2.3:a:nintendo:ds_wireless_communication:3:*:*:*:*:*:*:*|cpe:2.3:a:nintendo:ds_wireless_communication:11:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>nintendo</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3827,6 +4312,11 @@
           <t>cpe:2.3:a:sidequestvr:sidequest:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>oculus quest</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3860,6 +4350,11 @@
       <c r="G99" t="inlineStr">
         <is>
           <t>cpe:2.3:a:microsoft:xbox_gaming_services:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>xbox</t>
         </is>
       </c>
     </row>
@@ -3929,6 +4424,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.2:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.2:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.2:rc3:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.2:rc4:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.2:rc5:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.2:rc6:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.2:rc7:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>steam|valve</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3960,6 +4460,11 @@
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>nintendo</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4051,6 +4556,11 @@
       <c r="G102" t="inlineStr">
         <is>
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc3:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc4:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc5:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc6:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>valve</t>
         </is>
       </c>
     </row>
@@ -4156,6 +4666,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc3:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc4:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc5:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc6:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4235,6 +4750,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.11:-:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.11:rc3:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.11:rc4:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.11:rc5:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.11:rc6:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.11:rc7:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc3:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc4:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc5:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.13:rc6:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4277,6 +4797,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4308,6 +4833,11 @@
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>nintendo</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4339,6 +4869,11 @@
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4364,6 +4899,11 @@
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>playstation</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4406,6 +4946,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.0:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.0:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.0:rc3:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>nintendo</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4446,6 +4991,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.0:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.0:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.0:rc3:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>steam</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4482,6 +5032,11 @@
       <c r="G111" t="inlineStr">
         <is>
           <t>cpe:2.3:a:apache:tomcat:*:*:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone1:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone10:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone11:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone12:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone13:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone14:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone15:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone16:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone17:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone18:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone19:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone2:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone20:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone21:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone22:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone23:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone24:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone25:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone26:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone27:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone3:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone4:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone5:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone6:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone7:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone8:*:*:*:*:*:*|cpe:2.3:a:apache:tomcat:9.0.0:milestone9:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>valve</t>
         </is>
       </c>
     </row>
@@ -4528,6 +5083,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.16:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.16:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.16:rc3:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>nintendo</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4563,6 +5123,11 @@
           <t>cpe:2.3:o:microsoft:windows_10_1507:*:*:*:*:*:*:x64:*|cpe:2.3:o:microsoft:windows_10_1507:*:*:*:*:*:*:x86:*|cpe:2.3:o:microsoft:windows_10_1607:*:*:*:*:*:*:x64:*|cpe:2.3:o:microsoft:windows_10_1607:*:*:*:*:*:*:x86:*|cpe:2.3:o:microsoft:windows_10_1809:*:*:*:*:*:*:x64:*|cpe:2.3:o:microsoft:windows_10_1809:*:*:*:*:*:*:x86:*|cpe:2.3:o:microsoft:windows_10_21h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_10_22h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11_22h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11_23h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11_24h2:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows_11_25h2:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4596,6 +5161,11 @@
       <c r="G114" t="inlineStr">
         <is>
           <t>cpe:2.3:a:microsoft:xbox_gaming_services:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>xbox</t>
         </is>
       </c>
     </row>
@@ -4623,6 +5193,11 @@
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4658,6 +5233,11 @@
           <t>cpe:2.3:a:microsoft:xbox_gaming_services:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4691,6 +5271,11 @@
       <c r="G117" t="inlineStr">
         <is>
           <t>cpe:2.3:a:microsoft:xbox_gaming_services:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>xbox</t>
         </is>
       </c>
     </row>
@@ -4718,6 +5303,11 @@
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>playstation</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4746,6 +5336,11 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>xbox|steam</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4779,6 +5374,11 @@
       <c r="G120" t="inlineStr">
         <is>
           <t>cpe:2.3:a:openclaw:openclaw:*:*:*:*:*:node.js:*:*</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>ps4</t>
         </is>
       </c>
     </row>
@@ -4829,6 +5429,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:5.3.9:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:5.4:-:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:5.4:rc6:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:5.4:rc7:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:5.4:rc8:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc3:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.0:rc4:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4860,6 +5465,11 @@
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4891,6 +5501,11 @@
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>playstation</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4947,6 +5562,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4985,6 +5605,11 @@
       <c r="G125" t="inlineStr">
         <is>
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>playstation</t>
         </is>
       </c>
     </row>
@@ -5026,6 +5651,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.1:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.1:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:7.1:rc3:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>playstation</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5060,6 +5690,11 @@
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5091,6 +5726,11 @@
           <t>cpe:2.3:h:microsoft:xbox_360:4532:*:*:*:*:*:*:*|cpe:2.3:h:microsoft:xbox_360:4548:*:*:*:*:*:*:*|cpe:2.3:h:microsoft:xbox_360:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5122,6 +5762,11 @@
           <t>cpe:2.3:h:microsoft:xbox_360:4532:*:*:*:*:*:*:*|cpe:2.3:h:microsoft:xbox_360:4548:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5153,6 +5798,11 @@
           <t>cpe:2.3:h:sony:playstation_3:1.60:*:*:*:*:*:*:*|cpe:2.3:h:sony:playstation_portable:3.10_oe-a:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>playstation|ps3</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5188,6 +5838,11 @@
           <t>cpe:2.3:a:valvesoftware:counter-strike:1.6:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5221,6 +5876,11 @@
       <c r="G132" t="inlineStr">
         <is>
           <t>cpe:2.3:o:nintendo:game_boy_color_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:nintendo:game_boy_color:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>nintendo</t>
         </is>
       </c>
     </row>
